--- a/从零开始学Slots/从零开始学Slots-28-基础篇-SplittingSymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-28-基础篇-SplittingSymbols.xlsx
@@ -7876,6 +7876,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N177" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8644,5 +8647,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Q82" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>